--- a/bingo poker club 2026.xlsx
+++ b/bingo poker club 2026.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\.gemini\antigravity\scratch\bingo-poker-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCF6148-BD22-47F7-8C71-4C531C9EC49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11BE2A7F-4C0C-4EC2-B5E7-404CEE47247C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Posiciones" sheetId="1" r:id="rId1"/>
-    <sheet name="rake" sheetId="8" r:id="rId2"/>
-    <sheet name="Clasificacion de Puntos" sheetId="6" r:id="rId3"/>
+    <sheet name="rake" sheetId="2" r:id="rId2"/>
+    <sheet name="Clasificacion de Puntos" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
@@ -24,6 +24,7 @@
     <definedName name="TipoMesa">'[1]Calculo Puntaje'!$A$48:$A$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,39 +42,99 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+  <si>
+    <t>Bingo Poker Club</t>
+  </si>
+  <si>
+    <t>Ganancias Totales</t>
+  </si>
+  <si>
+    <t>Pos.</t>
+  </si>
   <si>
     <t>Jugador</t>
   </si>
   <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>FR</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Pos.</t>
+    <t>Robin</t>
+  </si>
+  <si>
+    <t>Posiciones</t>
+  </si>
+  <si>
+    <t>Alonso</t>
+  </si>
+  <si>
+    <t>Cobre</t>
+  </si>
+  <si>
+    <t>Mauro</t>
   </si>
   <si>
     <t>Diego</t>
   </si>
   <si>
-    <t>Mauro</t>
-  </si>
-  <si>
-    <t>Cobre</t>
-  </si>
-  <si>
-    <t>Robin</t>
-  </si>
-  <si>
-    <t>Fecha</t>
+    <t>Dany</t>
+  </si>
+  <si>
+    <t>F1</t>
   </si>
   <si>
     <t>F2</t>
   </si>
   <si>
-    <t>F1</t>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>F8</t>
   </si>
   <si>
     <t>F9</t>
@@ -82,42 +143,6 @@
     <t>F10</t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>Campeonato</t>
-  </si>
-  <si>
-    <t>Mesa Final</t>
-  </si>
-  <si>
-    <t>Ganancias Totales</t>
-  </si>
-  <si>
     <t>Lugar - Tipo de mesa</t>
   </si>
   <si>
@@ -152,74 +177,16 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>Posiciones</t>
-  </si>
-  <si>
-    <t>Alonso</t>
-  </si>
-  <si>
-    <t>Dany</t>
-  </si>
-  <si>
-    <t>Bingo Poker Club</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>F4</t>
-  </si>
-  <si>
-    <t>F5</t>
-  </si>
-  <si>
-    <t>F6</t>
-  </si>
-  <si>
-    <t>F7</t>
-  </si>
-  <si>
-    <t>F8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -336,11 +303,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFFFF00"/>
       <name val="Arial"/>
@@ -385,7 +347,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -637,177 +599,231 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="4" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="3" borderId="4" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="4" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="4" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="20" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 10" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 3 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 3 2 2 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 3 2 3" xfId="15" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 3 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 3 2 2 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Normal 3 2 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="Normal 3 3" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Normal 3 3 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normal 3 4" xfId="13" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Normal 4" xfId="4" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Normal 5" xfId="3" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 5 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Normal 5 2 2" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Normal 5 3" xfId="14" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Normal 6" xfId="7" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Normal 7" xfId="6" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Normal 7 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Normal 8" xfId="12" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Normal 9" xfId="11" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Normal 3 3 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 3 4" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 5 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal 5 2 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Normal 5 3" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 6" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 7" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 7 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normal 8" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 9" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFFCC00"/>
-      <color rgb="FFCC370E"/>
-      <color rgb="FFDD3B0F"/>
-      <color rgb="FFC3340D"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -839,7 +855,7 @@
         <xdr:cNvPr id="5" name="Imagen 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D32CFCBE-8B9E-48A7-901C-A37E6A0010B4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -861,6 +877,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -871,9 +890,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Calendario Liga"/>
       <sheetName val="Detalle por Fecha"/>
@@ -1216,394 +1232,393 @@
     <col min="23" max="23" width="4.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:19" ht="23.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="25"/>
-      <c r="Q2" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" s="39"/>
-      <c r="S2" s="40"/>
-    </row>
-    <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="26" t="s">
+    <row r="1" spans="2:19" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:19" ht="23.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="40"/>
+      <c r="Q2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="45"/>
+      <c r="S2" s="46"/>
+    </row>
+    <row r="3" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="I3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="N3" s="22">
+        <v>10</v>
+      </c>
+      <c r="O3" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="P3" s="3"/>
+      <c r="Q3" s="47">
+        <v>67500</v>
+      </c>
+      <c r="R3" s="48"/>
+      <c r="S3" s="49"/>
+    </row>
+    <row r="4" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="28">
-        <v>10</v>
-      </c>
-      <c r="O3" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="36">
-        <f>rake!L3</f>
-        <v>39000</v>
-      </c>
-      <c r="R3" s="41"/>
-      <c r="S3" s="42"/>
-    </row>
-    <row r="4" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="27"/>
+      <c r="F4" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="37"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="2:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="20">
+    <row r="5" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="19">
         <v>1</v>
       </c>
-      <c r="C5" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="35"/>
+      <c r="C5" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="27"/>
       <c r="E5" s="10">
         <v>50</v>
       </c>
-      <c r="F5" s="10"/>
+      <c r="F5" s="10">
+        <v>50</v>
+      </c>
       <c r="G5" s="10"/>
       <c r="H5" s="11"/>
-      <c r="I5" s="33"/>
+      <c r="I5" s="25"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="12"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="21">
-        <f>SUM(E5:N5)</f>
-        <v>50</v>
+      <c r="N5" s="25"/>
+      <c r="O5" s="20">
+        <v>100</v>
       </c>
       <c r="P5" s="2"/>
-      <c r="Q5" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="S5" s="22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="20">
+      <c r="Q5" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="R5" s="33">
+        <v>16875</v>
+      </c>
+      <c r="S5" s="21">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="19">
         <v>2</v>
       </c>
-      <c r="C6" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="35"/>
+      <c r="C6" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="27"/>
       <c r="E6" s="10">
         <v>35</v>
       </c>
-      <c r="F6" s="10"/>
+      <c r="F6" s="10">
+        <v>35</v>
+      </c>
       <c r="G6" s="10"/>
       <c r="H6" s="11"/>
-      <c r="I6" s="33"/>
+      <c r="I6" s="25"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
       <c r="M6" s="13"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="21">
-        <f>SUM(E6:N6)</f>
-        <v>35</v>
+      <c r="N6" s="25"/>
+      <c r="O6" s="20">
+        <v>70</v>
       </c>
       <c r="P6" s="2"/>
-      <c r="Q6" s="48">
+      <c r="Q6" s="34">
         <v>1</v>
       </c>
       <c r="R6" s="1">
-        <f>(Q3*60%)*50%</f>
-        <v>11700</v>
+        <v>10125</v>
       </c>
       <c r="S6" s="8">
-        <f>(Q3*30%)*50%</f>
-        <v>5850</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B7" s="20">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="19">
         <v>3</v>
       </c>
-      <c r="C7" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="35"/>
+      <c r="C7" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="27"/>
       <c r="E7" s="10">
+        <v>10</v>
+      </c>
+      <c r="F7" s="10">
         <v>20</v>
       </c>
-      <c r="F7" s="10"/>
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
-      <c r="I7" s="33"/>
+      <c r="I7" s="25"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="21">
-        <f>SUM(E7:N7)</f>
+      <c r="N7" s="25"/>
+      <c r="O7" s="20">
+        <v>30</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="34">
+        <v>2</v>
+      </c>
+      <c r="R7" s="1">
+        <v>6750</v>
+      </c>
+      <c r="S7" s="8">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="19">
+        <v>4</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="48">
-        <v>2</v>
-      </c>
-      <c r="R7" s="1">
-        <f>(Q3*60%)*30%</f>
-        <v>7020</v>
-      </c>
-      <c r="S7" s="8">
-        <f>(Q3*30%)*30%</f>
-        <v>3510</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="20">
-        <v>4</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="27"/>
       <c r="E8" s="10">
-        <v>10</v>
-      </c>
-      <c r="F8" s="10"/>
+        <v>20</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0</v>
+      </c>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
-      <c r="I8" s="33"/>
+      <c r="I8" s="25"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="13"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="21">
-        <f>SUM(E8:N8)</f>
-        <v>10</v>
+      <c r="N8" s="25"/>
+      <c r="O8" s="20">
+        <v>20</v>
       </c>
       <c r="P8" s="2"/>
-      <c r="Q8" s="49">
+      <c r="Q8" s="35">
         <v>3</v>
       </c>
       <c r="R8" s="6">
         <f>(Q3*60%)*20%</f>
-        <v>4680</v>
+        <v>8100</v>
       </c>
       <c r="S8" s="7">
         <f>(Q3*30%)*20%</f>
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="20">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="19">
         <v>5</v>
       </c>
-      <c r="C9" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="35"/>
+      <c r="C9" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="27"/>
       <c r="E9" s="10">
         <v>0</v>
       </c>
-      <c r="F9" s="10"/>
+      <c r="F9" s="10">
+        <v>10</v>
+      </c>
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="33"/>
+      <c r="I9" s="25"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="12"/>
       <c r="M9" s="13"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="21">
-        <f>SUM(E9:N9)</f>
-        <v>0</v>
+      <c r="N9" s="25"/>
+      <c r="O9" s="20">
+        <v>10</v>
       </c>
       <c r="P9" s="2"/>
     </row>
-    <row r="10" spans="2:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="20">
+    <row r="10" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="19">
         <v>6</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="35"/>
+      <c r="C10" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="27"/>
       <c r="E10" s="10">
         <v>0</v>
       </c>
-      <c r="F10" s="10"/>
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
       <c r="G10" s="10"/>
       <c r="H10" s="11"/>
-      <c r="I10" s="33"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="12"/>
       <c r="M10" s="13"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="21">
-        <f>SUM(E10:N10)</f>
+      <c r="N10" s="25"/>
+      <c r="O10" s="20">
         <v>0</v>
       </c>
       <c r="P10" s="2"/>
     </row>
-    <row r="11" spans="2:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="20">
+    <row r="11" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="19">
         <v>7</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="32"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="33"/>
+      <c r="I11" s="25"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="21"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="20"/>
       <c r="P11" s="2"/>
     </row>
-    <row r="12" spans="2:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P12" s="2"/>
     </row>
-    <row r="24" spans="19:19" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="19:19" ht="13" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="S25" s="37"/>
+    <row r="24" spans="19:19" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="19:19" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S25" s="28"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C5:O10">
-    <sortCondition descending="1" ref="O5:O10"/>
-  </sortState>
   <mergeCells count="8">
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="O3:O4"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="O3:O4"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="E3:M3" numberStoredAsText="1"/>
-  </ignoredErrors>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8744BD71-0880-49F5-B789-D3BA870B12E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:L3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:12" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:12" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="45" t="s">
-        <v>2</v>
+      <c r="B2" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>39000</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1">
+        <v>28500</v>
+      </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1613,78 +1628,76 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1">
-        <f>SUM(B3:K3)</f>
-        <v>39000</v>
+        <v>67500</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:8" ht="32.5" x14ac:dyDescent="0.65">
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-    </row>
-    <row r="2" spans="2:8" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" ht="32.5" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+    </row>
+    <row r="2" spans="2:8" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:8" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="17" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="17">
         <v>1</v>
       </c>
@@ -1707,7 +1720,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="17">
         <v>2</v>
       </c>
@@ -1730,12 +1743,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="17">
         <v>3</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D7" s="9">
         <v>20</v>
@@ -1744,7 +1757,7 @@
         <v>30</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G7" s="9">
         <v>40</v>
@@ -1753,12 +1766,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="17">
         <v>4</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" s="9">
         <v>10</v>
@@ -1767,7 +1780,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G8" s="9">
         <v>20</v>
@@ -1776,21 +1789,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="17">
         <v>5</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G9" s="9">
         <v>10</v>
